--- a/Task1.xlsx
+++ b/Task1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\Excel\Practice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\Excel\Task\LogicalMethod_Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03E5A79-049B-4F1E-BB25-CFBCC659198E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E403A7C-497E-4A30-B31E-C439DCE9D45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7EFEBD6F-ECEE-4635-90F8-4200A407ED5F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -301,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -325,20 +325,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -767,7 +761,7 @@
         <v>Can't Travel</v>
       </c>
       <c r="P5" s="2" t="str">
-        <f>IF(N5&lt;0,"Less Time",IF(N5=$N$6,"Perfect choice","Wait"))</f>
+        <f>IF(N5&lt;0,"Less Time",IF(N5=$I$20,"Perfect choice","Wait"))</f>
         <v>Wait</v>
       </c>
     </row>
@@ -819,7 +813,7 @@
         <v>Travel</v>
       </c>
       <c r="P6" s="2" t="str">
-        <f t="shared" ref="P6:P10" si="2">IF(N6&lt;0,"Less Time",IF(N6=$N$6,"Perfect choice","Wait"))</f>
+        <f t="shared" ref="P6:P10" si="2">IF(N6&lt;0,"Less Time",IF(N6=$I$20,"Perfect choice","Wait"))</f>
         <v>Perfect choice</v>
       </c>
     </row>
@@ -863,11 +857,11 @@
         <v>Low Budget</v>
       </c>
       <c r="N7" s="6">
-        <f t="shared" ref="N6:N10" si="3">I$12-J7</f>
+        <f t="shared" ref="N7:N10" si="3">I$12-J7</f>
         <v>0.51388888888888884</v>
       </c>
       <c r="O7" s="2" t="str">
-        <f t="shared" ref="O6:O10" si="4">IF(I$13&lt;N7,"Travel","Can't Travel")</f>
+        <f t="shared" ref="O7:O10" si="4">IF(I$13&lt;N7,"Travel","Can't Travel")</f>
         <v>Travel</v>
       </c>
       <c r="P7" s="2" t="str">
@@ -1052,7 +1046,7 @@
       <c r="F13">
         <v>80</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="4" t="s">
         <v>49</v>
       </c>
       <c r="I13" s="5">
@@ -1060,48 +1054,48 @@
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="14"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="17" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="9"/>
+      <c r="F17" s="12"/>
       <c r="H17" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="9"/>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="I18" s="9" t="s">
+      <c r="F18" s="12"/>
+      <c r="I18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="20" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="10">
         <f>_xlfn.MINIFS(N5:N10,O5:O10,"Travel")</f>
         <v>0.20833333333333326</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="8">
         <f>MATCH(I20,N5:N10)</f>
         <v>2</v>
       </c>
